--- a/artfynd/A 32348-2026 artfynd.xlsx
+++ b/artfynd/A 32348-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -788,9 +788,121 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>137259776</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91622</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Fridhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>548368</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6383272</v>
+      </c>
+      <c r="S3" t="n">
+        <v>15</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Sandig vägkant med tall.</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Viktor Åberg, Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137259776</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32348-2026 artfynd.xlsx
+++ b/artfynd/A 32348-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>137259776</v>
       </c>
       <c r="B3" t="n">
-        <v>91622</v>
+        <v>91632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32348-2026 artfynd.xlsx
+++ b/artfynd/A 32348-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>137259776</v>
       </c>
       <c r="B3" t="n">
-        <v>91632</v>
+        <v>91633</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,12 +884,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Viktor Leo</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Viktor Lund, Viktor Åberg, Jesper Hansson</t>
+          <t>Viktor Leo, Viktor Åberg, Jesper Hansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 32348-2026 artfynd.xlsx
+++ b/artfynd/A 32348-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>137259776</v>
       </c>
       <c r="B3" t="n">
-        <v>91633</v>
+        <v>91636</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32348-2026 artfynd.xlsx
+++ b/artfynd/A 32348-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>137259776</v>
       </c>
       <c r="B3" t="n">
-        <v>91636</v>
+        <v>91638</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32348-2026 artfynd.xlsx
+++ b/artfynd/A 32348-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>137259776</v>
       </c>
       <c r="B3" t="n">
-        <v>91638</v>
+        <v>91643</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32348-2026 artfynd.xlsx
+++ b/artfynd/A 32348-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>137259776</v>
       </c>
       <c r="B3" t="n">
-        <v>91643</v>
+        <v>91655</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32348-2026 artfynd.xlsx
+++ b/artfynd/A 32348-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,53 +680,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>87700130</v>
+        <v>137441442</v>
       </c>
       <c r="B2" t="n">
-        <v>58327</v>
+        <v>93498</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>2059</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Pelarnevägen, Tobo golfbana, Sm</t>
+          <t>Fridhem, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548452</v>
+        <v>548428</v>
       </c>
       <c r="R2" t="n">
-        <v>6383238</v>
+        <v>6383248</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,12 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,27 +775,27 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Fredrik Gustafsson</t>
+          <t>Viktor Åberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Fredrik Gustafsson</t>
+          <t>Viktor Åberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/87700130</t>
+          <t>https://artportalen.se/Sighting/137441442</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>137259776</v>
+        <v>137441433</v>
       </c>
       <c r="B3" t="n">
-        <v>91655</v>
+        <v>93520</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,40 +803,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>256703</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Fridhem, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548368</v>
+        <v>548432</v>
       </c>
       <c r="R3" t="n">
-        <v>6383272</v>
+        <v>6383257</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -858,12 +857,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,28 +881,243 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Sandig vägkant med tall.</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Viktor Leo</t>
+          <t>Viktor Åberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Viktor Leo, Viktor Åberg, Jesper Hansson</t>
+          <t>Viktor Åberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137441433</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>87700130</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Pelarnevägen, Tobo golfbana, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>548452</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6383238</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2020-08-27</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2020-08-27</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Fredrik Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Fredrik Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87700130</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>137259776</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91656</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Fridhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>548368</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6383272</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Sandig vägkant med tall.</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Viktor Leo</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Viktor Leo, Viktor Åberg, Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137259776</t>
         </is>
@@ -903,6 +1127,8 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32348-2026 artfynd.xlsx
+++ b/artfynd/A 32348-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137441442</v>
       </c>
       <c r="B2" t="n">
-        <v>93498</v>
+        <v>93501</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137441433</v>
       </c>
       <c r="B3" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>137259776</v>
       </c>
       <c r="B5" t="n">
-        <v>91656</v>
+        <v>91659</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 32348-2026 artfynd.xlsx
+++ b/artfynd/A 32348-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137441442</v>
       </c>
       <c r="B2" t="n">
-        <v>93501</v>
+        <v>93505</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137441433</v>
       </c>
       <c r="B3" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>137259776</v>
       </c>
       <c r="B5" t="n">
-        <v>91659</v>
+        <v>91663</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
